--- a/data/credenciais.xlsx
+++ b/data/credenciais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12B49821-7C66-4356-B0BD-77FCAF413F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9BF5BC-5797-4D22-B7FB-309AA40E5AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0606A66A-F90B-4FD7-84EC-19E6F9E010AB}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Senha</t>
   </si>
   <si>
-    <t>Unidade</t>
-  </si>
-  <si>
     <t>Adm</t>
   </si>
   <si>
@@ -189,6 +186,9 @@
   </si>
   <si>
     <t>CD FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>Operacao</t>
   </si>
 </sst>
 </file>
@@ -567,183 +567,183 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/credenciais.xlsx
+++ b/data/credenciais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9BF5BC-5797-4D22-B7FB-309AA40E5AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49AF91B-7098-4C19-A9CC-5FA78D6FADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0606A66A-F90B-4FD7-84EC-19E6F9E010AB}"/>
   </bookViews>
@@ -188,7 +188,7 @@
     <t>CD FOZ DO IGUAÇU</t>
   </si>
   <si>
-    <t>Operacao</t>
+    <t>Operação</t>
   </si>
 </sst>
 </file>
